--- a/products-storage/12-otvet-na-pretenziyu/41-reestr-garantiynyh-uderzhaniy.xlsx
+++ b/products-storage/12-otvet-na-pretenziyu/41-reestr-garantiynyh-uderzhaniy.xlsx
@@ -285,7 +285,7 @@
     </comment>
     <comment ref="H6" authorId="0" shapeId="0">
       <text>
-        <t>дата события; если событие не датируемое — красный флаг (см. чек-лист 06, С8: возврат должен быть привязан к событию, которым управляет субподрядчик)</t>
+        <t>дата события; если событие не датируемое — красный флаг (возврат должен быть привязан к событию, которым управляет субподрядчик)</t>
       </text>
     </comment>
     <comment ref="I6" authorId="0" shapeId="0">
@@ -4033,7 +4033,7 @@
     <row r="158" ht="46" customHeight="1">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>Красная строка — контрольная дата прошла, а возврат не запрошен. Жёлтая — до контрольной даты меньше порога, заданного на листе «Сводка». Событие возврата без даты — красный флаг само по себе: возврат должен быть привязан к событию, которым управляете вы (чек-лист 06, С8).</t>
+          <t>Красная строка — контрольная дата прошла, а возврат не запрошен. Жёлтая — до контрольной даты меньше порога, заданного на листе «Сводка». Событие возврата без даты — красный флаг само по себе: возврат должен быть привязан к событию, которым управляете вы.</t>
         </is>
       </c>
     </row>
@@ -4581,14 +4581,14 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>удержание не признаём, см. Т40 (17)</t>
+          <t>удержание не признаём, см. возражение на зачёт (файл 39)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Обратите внимание: у третьей строки контрольная дата пуста — событие возврата не привязано к дате. Это красный флаг из чек-листа 06 (С8), а не нормальное состояние строки.</t>
+          <t>Обратите внимание: у третьей строки контрольная дата пуста — событие возврата не привязано к дате. Это красный флаг, а не нормальное состояние строки.</t>
         </is>
       </c>
     </row>
